--- a/sources/ganryu_step6b.xlsx
+++ b/sources/ganryu_step6b.xlsx
@@ -728,6 +728,11 @@
           <t>Opponent can tech roll after the throw.</t>
         </is>
       </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>2a7ac50b-41fc-4e71-b0c5-5b89e00a22db</t>
+        </is>
+      </c>
       <c r="R6" t="inlineStr">
         <is>
           <t>2a7ac50b-41fc-4e71-b0c5-5b89e00a22db</t>
@@ -780,6 +785,11 @@
           <t>TRUE</t>
         </is>
       </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>772009bb-1ba2-4bed-a93b-b143fc09bbac</t>
+        </is>
+      </c>
       <c r="R7" t="inlineStr">
         <is>
           <t>772009bb-1ba2-4bed-a93b-b143fc09bbac</t>
@@ -832,6 +842,11 @@
           <t>TRUE</t>
         </is>
       </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>3a4f81fa-8568-40b0-912f-e46ef9153678</t>
+        </is>
+      </c>
       <c r="R8" t="inlineStr">
         <is>
           <t>3a4f81fa-8568-40b0-912f-e46ef9153678</t>
@@ -874,6 +889,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>5bc9fb38-18e7-401d-903c-7e16457c54ea</t>
+        </is>
+      </c>
       <c r="R9" t="inlineStr">
         <is>
           <t>5bc9fb38-18e7-401d-903c-7e16457c54ea</t>
@@ -919,6 +939,11 @@
       <c r="M10" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>06da1e67-d557-429d-bbe8-0414aa87e38a</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">

--- a/sources/ganryu_step6b.xlsx
+++ b/sources/ganryu_step6b.xlsx
@@ -2542,7 +2542,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Df+1,2,1</t>
+          <t>DF,1,2,1</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2604,7 +2604,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Df+2,1,2</t>
+          <t>DF,2,1,2</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -4481,6 +4481,11 @@
           <t>–– u</t>
         </is>
       </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>d</t>
+        </is>
+      </c>
       <c r="C76" t="inlineStr">
         <is>
           <t>–– Splits Side Step</t>
@@ -4845,6 +4850,11 @@
           <t>–– u</t>
         </is>
       </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>d</t>
+        </is>
+      </c>
       <c r="C83" t="inlineStr">
         <is>
           <t>–– Splits Side Step</t>
@@ -5135,6 +5145,11 @@
       <c r="A89" t="inlineStr">
         <is>
           <t>–– u</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>d</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
